--- a/PWMBoard/bom/PWMBoard.xlsx
+++ b/PWMBoard/bom/PWMBoard.xlsx
@@ -1,58 +1,45 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28623"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28827"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\yugod\Documents\ロボット研究部\基板\PWMBoard\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\yugod\Documents\ロボット研究部\基板\Robocon2025-PCB\GPIOBoard\bom\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3D00400E-0161-4085-91B0-931A9C60DFC6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{17C11B92-D41A-4A16-B099-73F751CCACF6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="14295" yWindow="0" windowWidth="14610" windowHeight="15585" xr2:uid="{EFC63906-D068-4AB2-83A7-32DDA7C987E9}"/>
+    <workbookView xWindow="270" yWindow="2730" windowWidth="28530" windowHeight="7485" xr2:uid="{D1C8D630-071C-4557-A661-2181C78AE700}"/>
   </bookViews>
   <sheets>
     <sheet name="PWMBoard" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029"/>
-  <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="166" uniqueCount="155">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="152" uniqueCount="147">
   <si>
     <t>Reference</t>
   </si>
   <si>
+    <t>Value</t>
+  </si>
+  <si>
+    <t>Name</t>
+  </si>
+  <si>
+    <t>URL</t>
+  </si>
+  <si>
+    <t>Price</t>
+  </si>
+  <si>
     <t>Qty</t>
   </si>
   <si>
-    <t>Value</t>
-  </si>
-  <si>
-    <t>Name</t>
-  </si>
-  <si>
-    <t>URL</t>
-  </si>
-  <si>
-    <t>Price</t>
-  </si>
-  <si>
     <t>C1</t>
   </si>
   <si>
@@ -101,6 +88,12 @@
     <t>1u</t>
   </si>
   <si>
+    <t>GRM188D71H105ME01W</t>
+  </si>
+  <si>
+    <t>https://www.digikey.jp/ja/products/detail/murata-electronics/GRM188D71H105ME01W/22528412</t>
+  </si>
+  <si>
     <t>C8,C9</t>
   </si>
   <si>
@@ -128,7 +121,7 @@
     <t>D2,D3,D4</t>
   </si>
   <si>
-    <t>CAN_RX,CAN_TX,Data</t>
+    <t>CAN_RX,CAN_TX,DATA</t>
   </si>
   <si>
     <t>SML-D14MWT86A</t>
@@ -191,15 +184,6 @@
     <t>https://www.digikey.jp/ja/products/detail/murata-electronics/BLM18KG601SN1D/1982766</t>
   </si>
   <si>
-    <t>H1,H2,H3,H4</t>
-  </si>
-  <si>
-    <t>MountingHole_Pad</t>
-  </si>
-  <si>
-    <t>-</t>
-  </si>
-  <si>
     <t>J1</t>
   </si>
   <si>
@@ -215,7 +199,7 @@
     <t>J2</t>
   </si>
   <si>
-    <t>Debug</t>
+    <t>DEBUG</t>
   </si>
   <si>
     <t>5077CR-16-SMC2-BK-TR</t>
@@ -260,12 +244,6 @@
     <t>https://akizukidenshi.com/catalog/g/g117949/</t>
   </si>
   <si>
-    <t>JP1,JP2</t>
-  </si>
-  <si>
-    <t>MCP2561/2FD selector,SolderJumper_3_Open</t>
-  </si>
-  <si>
     <t>R1,R21</t>
   </si>
   <si>
@@ -476,34 +454,13 @@
     <t>Y1</t>
   </si>
   <si>
-    <t>Crystal_GND2</t>
+    <t>32MHz</t>
   </si>
   <si>
     <t>XRCGB32M000F1SADR0</t>
   </si>
   <si>
     <t>https://www.digikey.jp/ja/products/detail/murata-electronics/XRCGB32M000F1SADR0/21662918?s=N4IgTCBcDaIBoCUDCBxAQgZjAWQAz4DEBGAZQEEARBXEAXQF8g</t>
-  </si>
-  <si>
-    <t>Price*Qty</t>
-    <phoneticPr fontId="18"/>
-  </si>
-  <si>
-    <t>-</t>
-    <phoneticPr fontId="18"/>
-  </si>
-  <si>
-    <t>合計</t>
-    <rPh sb="0" eb="2">
-      <t>ゴウケイ</t>
-    </rPh>
-    <phoneticPr fontId="18"/>
-  </si>
-  <si>
-    <t>GRM188D71H105ME01W</t>
-  </si>
-  <si>
-    <t>https://www.digikey.jp/ja/products/detail/murata-electronics/GRM188D71H105ME01W/22528412</t>
   </si>
 </sst>
 </file>
@@ -1477,14 +1434,11 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DA55D9F1-D7AB-42BB-88C4-5AAC17F31793}">
-  <dimension ref="A1:G43"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{35A5A6CD-D8C7-4CCB-8880-EDA9D7076A5E}">
+  <dimension ref="A1:F39"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
-  <cols>
-    <col min="5" max="5" width="38" customWidth="1"/>
-  </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1503,975 +1457,765 @@
       <c r="F1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.4">
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A2" t="s">
         <v>6</v>
       </c>
-      <c r="B2">
-        <v>1</v>
+      <c r="B2" t="s">
+        <v>7</v>
       </c>
       <c r="C2" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E2" t="s">
         <v>9</v>
       </c>
+      <c r="E2">
+        <v>30</v>
+      </c>
       <c r="F2">
-        <v>30</v>
-      </c>
-      <c r="G2">
-        <f>F2*B2</f>
-        <v>30</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A3" t="s">
         <v>10</v>
       </c>
-      <c r="B3">
-        <v>1</v>
+      <c r="B3" t="s">
+        <v>7</v>
       </c>
       <c r="C3" t="s">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="D3" t="s">
-        <v>11</v>
-      </c>
-      <c r="E3" t="s">
         <v>12</v>
       </c>
+      <c r="E3">
+        <v>19</v>
+      </c>
       <c r="F3">
-        <v>19</v>
-      </c>
-      <c r="G3">
-        <f t="shared" ref="G3:G41" si="0">F3*B3</f>
-        <v>19</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A4" t="s">
         <v>13</v>
       </c>
-      <c r="B4">
+      <c r="B4" t="s">
+        <v>14</v>
+      </c>
+      <c r="C4" t="s">
+        <v>15</v>
+      </c>
+      <c r="D4" t="s">
+        <v>16</v>
+      </c>
+      <c r="E4">
+        <v>36</v>
+      </c>
+      <c r="F4">
         <v>12</v>
       </c>
-      <c r="C4" t="s">
-        <v>14</v>
-      </c>
-      <c r="D4" t="s">
-        <v>15</v>
-      </c>
-      <c r="E4" t="s">
-        <v>16</v>
-      </c>
-      <c r="F4">
-        <v>36</v>
-      </c>
-      <c r="G4">
-        <f t="shared" si="0"/>
-        <v>432</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.4">
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A5" t="s">
         <v>17</v>
       </c>
-      <c r="B5">
-        <v>1</v>
+      <c r="B5" t="s">
+        <v>7</v>
       </c>
       <c r="C5" t="s">
-        <v>7</v>
+        <v>18</v>
       </c>
       <c r="D5" t="s">
-        <v>18</v>
-      </c>
-      <c r="E5" t="s">
         <v>19</v>
       </c>
+      <c r="E5">
+        <v>53</v>
+      </c>
       <c r="F5">
-        <v>53</v>
-      </c>
-      <c r="G5">
-        <f t="shared" si="0"/>
-        <v>53</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A6" t="s">
         <v>20</v>
       </c>
-      <c r="B6">
-        <v>1</v>
+      <c r="B6" t="s">
+        <v>21</v>
       </c>
       <c r="C6" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D6" t="s">
+        <v>23</v>
+      </c>
+      <c r="E6">
+        <v>47</v>
+      </c>
+      <c r="F6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A7" t="s">
+        <v>24</v>
+      </c>
+      <c r="B7" t="s">
+        <v>25</v>
+      </c>
+      <c r="C7" t="s">
+        <v>26</v>
+      </c>
+      <c r="D7" t="s">
+        <v>27</v>
+      </c>
+      <c r="E7">
+        <v>16</v>
+      </c>
+      <c r="F7">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A8" t="s">
+        <v>28</v>
+      </c>
+      <c r="B8" t="s">
+        <v>29</v>
+      </c>
+      <c r="C8" t="s">
+        <v>30</v>
+      </c>
+      <c r="D8" t="s">
+        <v>31</v>
+      </c>
+      <c r="E8">
+        <v>30</v>
+      </c>
+      <c r="F8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A9" t="s">
+        <v>32</v>
+      </c>
+      <c r="B9" t="s">
+        <v>33</v>
+      </c>
+      <c r="C9" t="s">
+        <v>34</v>
+      </c>
+      <c r="D9" t="s">
+        <v>35</v>
+      </c>
+      <c r="E9">
+        <v>53</v>
+      </c>
+      <c r="F9">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A10" t="s">
+        <v>36</v>
+      </c>
+      <c r="B10" t="s">
+        <v>37</v>
+      </c>
+      <c r="C10" t="s">
+        <v>38</v>
+      </c>
+      <c r="D10" t="s">
+        <v>39</v>
+      </c>
+      <c r="E10">
+        <v>30</v>
+      </c>
+      <c r="F10">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A11" t="s">
+        <v>40</v>
+      </c>
+      <c r="B11" t="s">
+        <v>29</v>
+      </c>
+      <c r="C11" t="s">
+        <v>41</v>
+      </c>
+      <c r="D11" t="s">
+        <v>42</v>
+      </c>
+      <c r="E11">
+        <v>48</v>
+      </c>
+      <c r="F11">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A12" t="s">
+        <v>43</v>
+      </c>
+      <c r="B12" t="s">
+        <v>29</v>
+      </c>
+      <c r="C12" t="s">
+        <v>44</v>
+      </c>
+      <c r="D12" t="s">
+        <v>45</v>
+      </c>
+      <c r="E12">
+        <v>30</v>
+      </c>
+      <c r="F12">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A13" t="s">
+        <v>46</v>
+      </c>
+      <c r="B13" t="s">
+        <v>47</v>
+      </c>
+      <c r="C13" t="s">
+        <v>48</v>
+      </c>
+      <c r="D13" t="s">
+        <v>49</v>
+      </c>
+      <c r="E13">
+        <v>20</v>
+      </c>
+      <c r="F13">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A14" t="s">
+        <v>50</v>
+      </c>
+      <c r="B14" t="s">
+        <v>51</v>
+      </c>
+      <c r="C14" t="s">
+        <v>52</v>
+      </c>
+      <c r="D14" t="s">
+        <v>53</v>
+      </c>
+      <c r="E14">
+        <v>16</v>
+      </c>
+      <c r="F14">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A15" t="s">
+        <v>54</v>
+      </c>
+      <c r="B15" t="s">
+        <v>55</v>
+      </c>
+      <c r="C15" t="s">
+        <v>56</v>
+      </c>
+      <c r="D15" t="s">
+        <v>57</v>
+      </c>
+      <c r="E15">
+        <v>81</v>
+      </c>
+      <c r="F15">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A16" t="s">
+        <v>58</v>
+      </c>
+      <c r="B16" t="s">
+        <v>59</v>
+      </c>
+      <c r="C16" t="s">
+        <v>60</v>
+      </c>
+      <c r="D16" t="s">
+        <v>61</v>
+      </c>
+      <c r="E16">
+        <v>110</v>
+      </c>
+      <c r="F16">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A17" t="s">
+        <v>62</v>
+      </c>
+      <c r="B17" t="s">
+        <v>63</v>
+      </c>
+      <c r="C17" t="s">
+        <v>64</v>
+      </c>
+      <c r="D17" t="s">
+        <v>65</v>
+      </c>
+      <c r="E17">
+        <v>62</v>
+      </c>
+      <c r="F17">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A18" t="s">
+        <v>66</v>
+      </c>
+      <c r="B18" t="s">
+        <v>67</v>
+      </c>
+      <c r="C18" t="s">
+        <v>68</v>
+      </c>
+      <c r="D18" t="s">
+        <v>69</v>
+      </c>
+      <c r="E18">
+        <v>59</v>
+      </c>
+      <c r="F18">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A19" t="s">
+        <v>70</v>
+      </c>
+      <c r="B19" t="s">
+        <v>71</v>
+      </c>
+      <c r="C19" t="s">
+        <v>72</v>
+      </c>
+      <c r="D19" t="s">
+        <v>73</v>
+      </c>
+      <c r="E19">
+        <v>70</v>
+      </c>
+      <c r="F19">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A20" t="s">
+        <v>74</v>
+      </c>
+      <c r="B20" s="1">
+        <v>420430</v>
+      </c>
+      <c r="C20" t="s">
+        <v>75</v>
+      </c>
+      <c r="D20" t="s">
+        <v>76</v>
+      </c>
+      <c r="E20">
+        <v>22</v>
+      </c>
+      <c r="F20">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A21" t="s">
+        <v>77</v>
+      </c>
+      <c r="B21">
+        <v>243</v>
+      </c>
+      <c r="C21" t="s">
+        <v>78</v>
+      </c>
+      <c r="D21" t="s">
+        <v>79</v>
+      </c>
+      <c r="E21">
+        <v>22</v>
+      </c>
+      <c r="F21">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A22" t="s">
+        <v>80</v>
+      </c>
+      <c r="B22" t="s">
+        <v>81</v>
+      </c>
+      <c r="C22" t="s">
+        <v>82</v>
+      </c>
+      <c r="D22" t="s">
+        <v>83</v>
+      </c>
+      <c r="E22">
+        <v>22</v>
+      </c>
+      <c r="F22">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A23" t="s">
+        <v>84</v>
+      </c>
+      <c r="B23" t="s">
+        <v>85</v>
+      </c>
+      <c r="C23" t="s">
+        <v>86</v>
+      </c>
+      <c r="D23" t="s">
+        <v>87</v>
+      </c>
+      <c r="E23">
+        <v>22</v>
+      </c>
+      <c r="F23">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A24" t="s">
+        <v>88</v>
+      </c>
+      <c r="B24">
+        <v>600</v>
+      </c>
+      <c r="C24" t="s">
+        <v>89</v>
+      </c>
+      <c r="D24" t="s">
+        <v>90</v>
+      </c>
+      <c r="E24">
+        <v>22</v>
+      </c>
+      <c r="F24">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A25" t="s">
+        <v>91</v>
+      </c>
+      <c r="B25">
+        <v>300</v>
+      </c>
+      <c r="C25" t="s">
+        <v>92</v>
+      </c>
+      <c r="D25" t="s">
+        <v>93</v>
+      </c>
+      <c r="E25">
+        <v>22</v>
+      </c>
+      <c r="F25">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="26" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A26" t="s">
+        <v>94</v>
+      </c>
+      <c r="B26">
+        <v>120</v>
+      </c>
+      <c r="C26" t="s">
+        <v>95</v>
+      </c>
+      <c r="D26" t="s">
+        <v>96</v>
+      </c>
+      <c r="E26">
+        <v>22</v>
+      </c>
+      <c r="F26">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="27" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A27" t="s">
+        <v>97</v>
+      </c>
+      <c r="B27">
+        <v>80</v>
+      </c>
+      <c r="C27" t="s">
+        <v>98</v>
+      </c>
+      <c r="D27" t="s">
+        <v>99</v>
+      </c>
+      <c r="E27">
+        <v>22</v>
+      </c>
+      <c r="F27">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="28" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A28" t="s">
+        <v>100</v>
+      </c>
+      <c r="B28" t="s">
+        <v>101</v>
+      </c>
+      <c r="C28" t="s">
+        <v>102</v>
+      </c>
+      <c r="D28" t="s">
+        <v>103</v>
+      </c>
+      <c r="E28">
+        <v>22</v>
+      </c>
+      <c r="F28">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="29" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A29" t="s">
+        <v>104</v>
+      </c>
+      <c r="B29" t="s">
+        <v>105</v>
+      </c>
+      <c r="C29" t="s">
+        <v>106</v>
+      </c>
+      <c r="D29" t="s">
+        <v>107</v>
+      </c>
+      <c r="E29">
+        <v>22</v>
+      </c>
+      <c r="F29">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="30" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A30" t="s">
+        <v>108</v>
+      </c>
+      <c r="B30" t="s">
+        <v>109</v>
+      </c>
+      <c r="C30" t="s">
+        <v>110</v>
+      </c>
+      <c r="D30" t="s">
+        <v>111</v>
+      </c>
+      <c r="E30">
+        <v>458</v>
+      </c>
+      <c r="F30">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="31" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A31" t="s">
+        <v>112</v>
+      </c>
+      <c r="B31" t="s">
+        <v>113</v>
+      </c>
+      <c r="C31" t="s">
+        <v>114</v>
+      </c>
+      <c r="D31" t="s">
+        <v>115</v>
+      </c>
+      <c r="E31">
+        <v>87</v>
+      </c>
+      <c r="F31">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="32" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A32" t="s">
+        <v>116</v>
+      </c>
+      <c r="B32" t="s">
+        <v>117</v>
+      </c>
+      <c r="C32" t="s">
+        <v>118</v>
+      </c>
+      <c r="D32" t="s">
+        <v>119</v>
+      </c>
+      <c r="E32">
+        <v>63</v>
+      </c>
+      <c r="F32">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="33" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A33" t="s">
+        <v>120</v>
+      </c>
+      <c r="B33" t="s">
+        <v>121</v>
+      </c>
+      <c r="C33" t="s">
+        <v>122</v>
+      </c>
+      <c r="D33" t="s">
+        <v>123</v>
+      </c>
+      <c r="E33">
+        <v>780</v>
+      </c>
+      <c r="F33">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="34" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A34" t="s">
+        <v>124</v>
+      </c>
+      <c r="B34" t="s">
+        <v>125</v>
+      </c>
+      <c r="C34" t="s">
+        <v>126</v>
+      </c>
+      <c r="D34" t="s">
+        <v>127</v>
+      </c>
+      <c r="E34">
         <v>153</v>
       </c>
-      <c r="E6" t="s">
-        <v>154</v>
-      </c>
-      <c r="F6">
-        <v>47</v>
-      </c>
-      <c r="G6">
-        <f t="shared" si="0"/>
-        <v>47</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.4">
-      <c r="A7" t="s">
-        <v>22</v>
-      </c>
-      <c r="B7">
+      <c r="F34">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="35" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A35" t="s">
+        <v>128</v>
+      </c>
+      <c r="B35" t="s">
+        <v>129</v>
+      </c>
+      <c r="C35" t="s">
+        <v>130</v>
+      </c>
+      <c r="D35" t="s">
+        <v>131</v>
+      </c>
+      <c r="E35">
+        <v>339</v>
+      </c>
+      <c r="F35">
         <v>2</v>
       </c>
-      <c r="C7" t="s">
-        <v>23</v>
-      </c>
-      <c r="D7" t="s">
-        <v>24</v>
-      </c>
-      <c r="E7" t="s">
-        <v>25</v>
-      </c>
-      <c r="F7">
-        <v>16</v>
-      </c>
-      <c r="G7">
-        <f t="shared" si="0"/>
-        <v>32</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.4">
-      <c r="A8" t="s">
-        <v>26</v>
-      </c>
-      <c r="B8">
-        <v>1</v>
-      </c>
-      <c r="C8" t="s">
-        <v>27</v>
-      </c>
-      <c r="D8" t="s">
-        <v>28</v>
-      </c>
-      <c r="E8" t="s">
-        <v>29</v>
-      </c>
-      <c r="F8">
+    </row>
+    <row r="36" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A36" t="s">
+        <v>132</v>
+      </c>
+      <c r="B36" t="s">
+        <v>133</v>
+      </c>
+      <c r="C36" t="s">
+        <v>133</v>
+      </c>
+      <c r="D36" t="s">
+        <v>134</v>
+      </c>
+      <c r="E36">
+        <v>90</v>
+      </c>
+      <c r="F36">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="37" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A37" t="s">
+        <v>135</v>
+      </c>
+      <c r="B37" t="s">
+        <v>136</v>
+      </c>
+      <c r="C37" t="s">
+        <v>137</v>
+      </c>
+      <c r="D37" t="s">
+        <v>138</v>
+      </c>
+      <c r="E37">
+        <v>244</v>
+      </c>
+      <c r="F37">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="38" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A38" t="s">
+        <v>139</v>
+      </c>
+      <c r="B38" t="s">
+        <v>140</v>
+      </c>
+      <c r="C38" t="s">
+        <v>141</v>
+      </c>
+      <c r="D38" t="s">
+        <v>142</v>
+      </c>
+      <c r="E38">
         <v>30</v>
       </c>
-      <c r="G8">
-        <f t="shared" si="0"/>
-        <v>30</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.4">
-      <c r="A9" t="s">
-        <v>30</v>
-      </c>
-      <c r="B9">
-        <v>3</v>
-      </c>
-      <c r="C9" t="s">
-        <v>31</v>
-      </c>
-      <c r="D9" t="s">
-        <v>32</v>
-      </c>
-      <c r="E9" t="s">
-        <v>33</v>
-      </c>
-      <c r="F9">
-        <v>53</v>
-      </c>
-      <c r="G9">
-        <f t="shared" si="0"/>
-        <v>159</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.4">
-      <c r="A10" t="s">
-        <v>34</v>
-      </c>
-      <c r="B10">
-        <v>3</v>
-      </c>
-      <c r="C10" t="s">
-        <v>35</v>
-      </c>
-      <c r="D10" t="s">
-        <v>36</v>
-      </c>
-      <c r="E10" t="s">
-        <v>37</v>
-      </c>
-      <c r="F10">
-        <v>30</v>
-      </c>
-      <c r="G10">
-        <f t="shared" si="0"/>
-        <v>90</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.4">
-      <c r="A11" t="s">
-        <v>38</v>
-      </c>
-      <c r="B11">
-        <v>9</v>
-      </c>
-      <c r="C11" t="s">
-        <v>27</v>
-      </c>
-      <c r="D11" t="s">
-        <v>39</v>
-      </c>
-      <c r="E11" t="s">
-        <v>40</v>
-      </c>
-      <c r="F11">
-        <v>48</v>
-      </c>
-      <c r="G11">
-        <f t="shared" si="0"/>
-        <v>432</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.4">
-      <c r="A12" t="s">
-        <v>41</v>
-      </c>
-      <c r="B12">
-        <v>1</v>
-      </c>
-      <c r="C12" t="s">
-        <v>27</v>
-      </c>
-      <c r="D12" t="s">
-        <v>42</v>
-      </c>
-      <c r="E12" t="s">
-        <v>43</v>
-      </c>
-      <c r="F12">
-        <v>30</v>
-      </c>
-      <c r="G12">
-        <f t="shared" si="0"/>
-        <v>30</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.4">
-      <c r="A13" t="s">
-        <v>44</v>
-      </c>
-      <c r="B13">
-        <v>2</v>
-      </c>
-      <c r="C13" t="s">
-        <v>45</v>
-      </c>
-      <c r="D13" t="s">
-        <v>46</v>
-      </c>
-      <c r="E13" t="s">
-        <v>47</v>
-      </c>
-      <c r="F13">
-        <v>20</v>
-      </c>
-      <c r="G13">
-        <f t="shared" si="0"/>
-        <v>40</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.4">
-      <c r="A14" t="s">
-        <v>48</v>
-      </c>
-      <c r="B14">
-        <v>1</v>
-      </c>
-      <c r="C14" t="s">
-        <v>49</v>
-      </c>
-      <c r="D14" t="s">
-        <v>50</v>
-      </c>
-      <c r="E14" t="s">
-        <v>51</v>
-      </c>
-      <c r="F14">
-        <v>16</v>
-      </c>
-      <c r="G14">
-        <f t="shared" si="0"/>
-        <v>16</v>
-      </c>
-    </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.4">
-      <c r="A15" t="s">
+      <c r="F38">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="39" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A39" t="s">
+        <v>143</v>
+      </c>
+      <c r="B39" t="s">
+        <v>144</v>
+      </c>
+      <c r="C39" t="s">
+        <v>145</v>
+      </c>
+      <c r="D39" t="s">
+        <v>146</v>
+      </c>
+      <c r="E39">
         <v>52</v>
       </c>
-      <c r="B15">
-        <v>4</v>
-      </c>
-      <c r="C15" t="s">
-        <v>53</v>
-      </c>
-      <c r="D15" t="s">
-        <v>54</v>
-      </c>
-      <c r="E15" t="s">
-        <v>54</v>
-      </c>
-      <c r="F15" t="s">
-        <v>54</v>
-      </c>
-      <c r="G15" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.4">
-      <c r="A16" t="s">
-        <v>55</v>
-      </c>
-      <c r="B16">
-        <v>1</v>
-      </c>
-      <c r="C16" t="s">
-        <v>56</v>
-      </c>
-      <c r="D16" t="s">
-        <v>57</v>
-      </c>
-      <c r="E16" t="s">
-        <v>58</v>
-      </c>
-      <c r="F16">
-        <v>81</v>
-      </c>
-      <c r="G16">
-        <f t="shared" si="0"/>
-        <v>81</v>
-      </c>
-    </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.4">
-      <c r="A17" t="s">
-        <v>59</v>
-      </c>
-      <c r="B17">
-        <v>1</v>
-      </c>
-      <c r="C17" t="s">
-        <v>60</v>
-      </c>
-      <c r="D17" t="s">
-        <v>61</v>
-      </c>
-      <c r="E17" t="s">
-        <v>62</v>
-      </c>
-      <c r="F17">
-        <v>110</v>
-      </c>
-      <c r="G17">
-        <f t="shared" si="0"/>
-        <v>110</v>
-      </c>
-    </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.4">
-      <c r="A18" t="s">
-        <v>63</v>
-      </c>
-      <c r="B18">
-        <v>1</v>
-      </c>
-      <c r="C18" t="s">
-        <v>64</v>
-      </c>
-      <c r="D18" t="s">
-        <v>65</v>
-      </c>
-      <c r="E18" t="s">
-        <v>66</v>
-      </c>
-      <c r="F18">
-        <v>62</v>
-      </c>
-      <c r="G18">
-        <f t="shared" si="0"/>
-        <v>62</v>
-      </c>
-    </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.4">
-      <c r="A19" t="s">
-        <v>67</v>
-      </c>
-      <c r="B19">
-        <v>8</v>
-      </c>
-      <c r="C19" t="s">
-        <v>68</v>
-      </c>
-      <c r="D19" t="s">
-        <v>69</v>
-      </c>
-      <c r="E19" t="s">
-        <v>70</v>
-      </c>
-      <c r="F19">
-        <v>59</v>
-      </c>
-      <c r="G19">
-        <f t="shared" si="0"/>
-        <v>472</v>
-      </c>
-    </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.4">
-      <c r="A20" t="s">
-        <v>71</v>
-      </c>
-      <c r="B20">
-        <v>1</v>
-      </c>
-      <c r="C20" t="s">
-        <v>72</v>
-      </c>
-      <c r="D20" t="s">
-        <v>73</v>
-      </c>
-      <c r="E20" t="s">
-        <v>74</v>
-      </c>
-      <c r="F20">
-        <v>70</v>
-      </c>
-      <c r="G20">
-        <f t="shared" si="0"/>
-        <v>70</v>
-      </c>
-    </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.4">
-      <c r="A21" t="s">
-        <v>75</v>
-      </c>
-      <c r="B21">
-        <v>2</v>
-      </c>
-      <c r="C21" t="s">
-        <v>76</v>
-      </c>
-      <c r="D21" t="s">
-        <v>54</v>
-      </c>
-      <c r="E21" t="s">
-        <v>54</v>
-      </c>
-      <c r="F21" t="s">
-        <v>54</v>
-      </c>
-      <c r="G21" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.4">
-      <c r="A22" t="s">
-        <v>77</v>
-      </c>
-      <c r="B22">
-        <v>2</v>
-      </c>
-      <c r="C22" s="1">
-        <v>420430</v>
-      </c>
-      <c r="D22" t="s">
-        <v>78</v>
-      </c>
-      <c r="E22" t="s">
-        <v>79</v>
-      </c>
-      <c r="F22">
-        <v>22</v>
-      </c>
-      <c r="G22">
-        <f t="shared" si="0"/>
-        <v>44</v>
-      </c>
-    </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.4">
-      <c r="A23" t="s">
-        <v>80</v>
-      </c>
-      <c r="B23">
-        <v>1</v>
-      </c>
-      <c r="C23">
-        <v>243</v>
-      </c>
-      <c r="D23" t="s">
-        <v>81</v>
-      </c>
-      <c r="E23" t="s">
-        <v>82</v>
-      </c>
-      <c r="F23">
-        <v>22</v>
-      </c>
-      <c r="G23">
-        <f t="shared" si="0"/>
-        <v>22</v>
-      </c>
-    </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.4">
-      <c r="A24" t="s">
-        <v>83</v>
-      </c>
-      <c r="B24">
-        <v>4</v>
-      </c>
-      <c r="C24" t="s">
-        <v>84</v>
-      </c>
-      <c r="D24" t="s">
-        <v>85</v>
-      </c>
-      <c r="E24" t="s">
-        <v>86</v>
-      </c>
-      <c r="F24">
-        <v>22</v>
-      </c>
-      <c r="G24">
-        <f t="shared" si="0"/>
-        <v>88</v>
-      </c>
-    </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.4">
-      <c r="A25" t="s">
-        <v>87</v>
-      </c>
-      <c r="B25">
-        <v>2</v>
-      </c>
-      <c r="C25" t="s">
-        <v>88</v>
-      </c>
-      <c r="D25" t="s">
-        <v>89</v>
-      </c>
-      <c r="E25" t="s">
-        <v>90</v>
-      </c>
-      <c r="F25">
-        <v>22</v>
-      </c>
-      <c r="G25">
-        <f t="shared" si="0"/>
-        <v>44</v>
-      </c>
-    </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.4">
-      <c r="A26" t="s">
-        <v>91</v>
-      </c>
-      <c r="B26">
-        <v>1</v>
-      </c>
-      <c r="C26">
-        <v>600</v>
-      </c>
-      <c r="D26" t="s">
-        <v>92</v>
-      </c>
-      <c r="E26" t="s">
-        <v>93</v>
-      </c>
-      <c r="F26">
-        <v>22</v>
-      </c>
-      <c r="G26">
-        <f t="shared" si="0"/>
-        <v>22</v>
-      </c>
-    </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.4">
-      <c r="A27" t="s">
-        <v>94</v>
-      </c>
-      <c r="B27">
-        <v>1</v>
-      </c>
-      <c r="C27">
-        <v>300</v>
-      </c>
-      <c r="D27" t="s">
-        <v>95</v>
-      </c>
-      <c r="E27" t="s">
-        <v>96</v>
-      </c>
-      <c r="F27">
-        <v>22</v>
-      </c>
-      <c r="G27">
-        <f t="shared" si="0"/>
-        <v>22</v>
-      </c>
-    </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.4">
-      <c r="A28" t="s">
-        <v>97</v>
-      </c>
-      <c r="B28">
-        <v>1</v>
-      </c>
-      <c r="C28">
-        <v>120</v>
-      </c>
-      <c r="D28" t="s">
-        <v>98</v>
-      </c>
-      <c r="E28" t="s">
-        <v>99</v>
-      </c>
-      <c r="F28">
-        <v>22</v>
-      </c>
-      <c r="G28">
-        <f t="shared" si="0"/>
-        <v>22</v>
-      </c>
-    </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.4">
-      <c r="A29" t="s">
-        <v>100</v>
-      </c>
-      <c r="B29">
-        <v>8</v>
-      </c>
-      <c r="C29">
-        <v>80</v>
-      </c>
-      <c r="D29" t="s">
-        <v>101</v>
-      </c>
-      <c r="E29" t="s">
-        <v>102</v>
-      </c>
-      <c r="F29">
-        <v>22</v>
-      </c>
-      <c r="G29">
-        <f t="shared" si="0"/>
-        <v>176</v>
-      </c>
-    </row>
-    <row r="30" spans="1:7" x14ac:dyDescent="0.4">
-      <c r="A30" t="s">
-        <v>103</v>
-      </c>
-      <c r="B30">
-        <v>2</v>
-      </c>
-      <c r="C30" t="s">
-        <v>104</v>
-      </c>
-      <c r="D30" t="s">
-        <v>105</v>
-      </c>
-      <c r="E30" t="s">
-        <v>106</v>
-      </c>
-      <c r="F30">
-        <v>22</v>
-      </c>
-      <c r="G30">
-        <f t="shared" si="0"/>
-        <v>44</v>
-      </c>
-    </row>
-    <row r="31" spans="1:7" x14ac:dyDescent="0.4">
-      <c r="A31" t="s">
-        <v>107</v>
-      </c>
-      <c r="B31">
-        <v>1</v>
-      </c>
-      <c r="C31" t="s">
-        <v>108</v>
-      </c>
-      <c r="D31" t="s">
-        <v>109</v>
-      </c>
-      <c r="E31" t="s">
-        <v>110</v>
-      </c>
-      <c r="F31">
-        <v>22</v>
-      </c>
-      <c r="G31">
-        <f t="shared" si="0"/>
-        <v>22</v>
-      </c>
-    </row>
-    <row r="32" spans="1:7" x14ac:dyDescent="0.4">
-      <c r="A32" t="s">
-        <v>111</v>
-      </c>
-      <c r="B32">
-        <v>1</v>
-      </c>
-      <c r="C32" t="s">
-        <v>112</v>
-      </c>
-      <c r="D32" t="s">
-        <v>113</v>
-      </c>
-      <c r="E32" t="s">
-        <v>114</v>
-      </c>
-      <c r="F32">
-        <v>458</v>
-      </c>
-      <c r="G32">
-        <f t="shared" si="0"/>
-        <v>458</v>
-      </c>
-    </row>
-    <row r="33" spans="1:7" x14ac:dyDescent="0.4">
-      <c r="A33" t="s">
-        <v>115</v>
-      </c>
-      <c r="B33">
-        <v>1</v>
-      </c>
-      <c r="C33" t="s">
-        <v>116</v>
-      </c>
-      <c r="D33" t="s">
-        <v>117</v>
-      </c>
-      <c r="E33" t="s">
-        <v>118</v>
-      </c>
-      <c r="F33">
-        <v>87</v>
-      </c>
-      <c r="G33">
-        <f t="shared" si="0"/>
-        <v>87</v>
-      </c>
-    </row>
-    <row r="34" spans="1:7" x14ac:dyDescent="0.4">
-      <c r="A34" t="s">
-        <v>119</v>
-      </c>
-      <c r="B34">
-        <v>1</v>
-      </c>
-      <c r="C34" t="s">
-        <v>120</v>
-      </c>
-      <c r="D34" t="s">
-        <v>121</v>
-      </c>
-      <c r="E34" t="s">
-        <v>122</v>
-      </c>
-      <c r="F34">
-        <v>63</v>
-      </c>
-      <c r="G34">
-        <f t="shared" si="0"/>
-        <v>63</v>
-      </c>
-    </row>
-    <row r="35" spans="1:7" x14ac:dyDescent="0.4">
-      <c r="A35" t="s">
-        <v>123</v>
-      </c>
-      <c r="B35">
-        <v>1</v>
-      </c>
-      <c r="C35" t="s">
-        <v>124</v>
-      </c>
-      <c r="D35" t="s">
-        <v>125</v>
-      </c>
-      <c r="E35" t="s">
-        <v>126</v>
-      </c>
-      <c r="F35">
-        <v>780</v>
-      </c>
-      <c r="G35">
-        <f t="shared" si="0"/>
-        <v>780</v>
-      </c>
-    </row>
-    <row r="36" spans="1:7" x14ac:dyDescent="0.4">
-      <c r="A36" t="s">
-        <v>127</v>
-      </c>
-      <c r="B36">
-        <v>1</v>
-      </c>
-      <c r="C36" t="s">
-        <v>128</v>
-      </c>
-      <c r="D36" t="s">
-        <v>129</v>
-      </c>
-      <c r="E36" t="s">
-        <v>130</v>
-      </c>
-      <c r="F36">
-        <v>153</v>
-      </c>
-      <c r="G36">
-        <f t="shared" si="0"/>
-        <v>153</v>
-      </c>
-    </row>
-    <row r="37" spans="1:7" x14ac:dyDescent="0.4">
-      <c r="A37" t="s">
-        <v>131</v>
-      </c>
-      <c r="B37">
-        <v>2</v>
-      </c>
-      <c r="C37" t="s">
-        <v>132</v>
-      </c>
-      <c r="D37" t="s">
-        <v>133</v>
-      </c>
-      <c r="E37" t="s">
-        <v>134</v>
-      </c>
-      <c r="F37">
-        <v>339</v>
-      </c>
-      <c r="G37">
-        <f t="shared" si="0"/>
-        <v>678</v>
-      </c>
-    </row>
-    <row r="38" spans="1:7" x14ac:dyDescent="0.4">
-      <c r="A38" t="s">
-        <v>135</v>
-      </c>
-      <c r="B38">
-        <v>1</v>
-      </c>
-      <c r="C38" t="s">
-        <v>136</v>
-      </c>
-      <c r="D38" t="s">
-        <v>136</v>
-      </c>
-      <c r="E38" t="s">
-        <v>137</v>
-      </c>
-      <c r="F38">
-        <v>90</v>
-      </c>
-      <c r="G38">
-        <f t="shared" si="0"/>
-        <v>90</v>
-      </c>
-    </row>
-    <row r="39" spans="1:7" x14ac:dyDescent="0.4">
-      <c r="A39" t="s">
-        <v>138</v>
-      </c>
-      <c r="B39">
-        <v>1</v>
-      </c>
-      <c r="C39" t="s">
-        <v>139</v>
-      </c>
-      <c r="D39" t="s">
-        <v>140</v>
-      </c>
-      <c r="E39" t="s">
-        <v>141</v>
-      </c>
       <c r="F39">
-        <v>244</v>
-      </c>
-      <c r="G39">
-        <f t="shared" si="0"/>
-        <v>244</v>
-      </c>
-    </row>
-    <row r="40" spans="1:7" x14ac:dyDescent="0.4">
-      <c r="A40" t="s">
-        <v>142</v>
-      </c>
-      <c r="B40">
-        <v>1</v>
-      </c>
-      <c r="C40" t="s">
-        <v>143</v>
-      </c>
-      <c r="D40" t="s">
-        <v>144</v>
-      </c>
-      <c r="E40" t="s">
-        <v>145</v>
-      </c>
-      <c r="F40">
-        <v>30</v>
-      </c>
-      <c r="G40">
-        <f t="shared" si="0"/>
-        <v>30</v>
-      </c>
-    </row>
-    <row r="41" spans="1:7" x14ac:dyDescent="0.4">
-      <c r="A41" t="s">
-        <v>146</v>
-      </c>
-      <c r="B41">
-        <v>1</v>
-      </c>
-      <c r="C41" t="s">
-        <v>147</v>
-      </c>
-      <c r="D41" t="s">
-        <v>148</v>
-      </c>
-      <c r="E41" t="s">
-        <v>149</v>
-      </c>
-      <c r="F41">
-        <v>52</v>
-      </c>
-      <c r="G41">
-        <f t="shared" si="0"/>
-        <v>52</v>
-      </c>
-    </row>
-    <row r="43" spans="1:7" x14ac:dyDescent="0.4">
-      <c r="F43" t="s">
-        <v>152</v>
-      </c>
-      <c r="G43">
-        <f>SUM(G2:G41)</f>
-        <v>5346</v>
+        <v>1</v>
       </c>
     </row>
   </sheetData>
